--- a/SB3_tests/BBC/bbc_summary_metrics.xlsx
+++ b/SB3_tests/BBC/bbc_summary_metrics.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,6 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,12 +472,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Overshoot (V)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>run_name</t>
+          <t>Real Overshoot (V)</t>
         </is>
       </c>
     </row>
@@ -495,19 +489,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3241.606678</v>
+        <v>4360.844031203538</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.005994573244089537</v>
+      </c>
       <c r="G2" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.33674190160272</v>
       </c>
     </row>
     <row r="3">
@@ -523,19 +514,16 @@
         <v>0.001</v>
       </c>
       <c r="D3" t="n">
-        <v>3242.1131194</v>
+        <v>4360.844036806375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.006101344503325805</v>
+      </c>
       <c r="G3" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.33674190162512</v>
       </c>
     </row>
     <row r="4">
@@ -551,19 +539,16 @@
         <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>3242.5902914</v>
+        <v>4360.948740590364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.01112239662565145</v>
+      </c>
       <c r="G4" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.33411037797238</v>
       </c>
     </row>
     <row r="5">
@@ -579,19 +564,16 @@
         <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-941.1559734</v>
+        <v>4364.283493865281</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03302000000000001</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0.0026</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005799105331187916</v>
+      </c>
       <c r="G5" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.34249657405651</v>
       </c>
     </row>
     <row r="6">
@@ -607,19 +589,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7.498788</v>
+        <v>4338.47444504546</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0.00923</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1316403671838796</v>
+      </c>
       <c r="G6" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>98.69644747121845</v>
       </c>
     </row>
     <row r="7">
@@ -635,19 +614,16 @@
         <v>0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>7.498788</v>
+        <v>4338.47444504546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0.00923</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1316403671838796</v>
+      </c>
       <c r="G7" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>98.69644747121845</v>
       </c>
     </row>
     <row r="8">
@@ -663,19 +639,16 @@
         <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>-185.8635298</v>
+        <v>4338.47444504546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4217460000000001</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0.00923</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1316403671838796</v>
+      </c>
       <c r="G8" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>98.69644747121845</v>
       </c>
     </row>
     <row r="9">
@@ -691,19 +664,14 @@
         <v>0.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-992.4983909999999</v>
+        <v>-735.7867907523178</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02886000000000001</v>
+        <v>0.04134</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>100.2505162616509</v>
       </c>
     </row>
     <row r="10">
@@ -719,19 +687,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-993.661658</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E10" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G10" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="11">
@@ -747,19 +712,16 @@
         <v>0.001</v>
       </c>
       <c r="D11" t="n">
-        <v>-993.661658</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G11" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="12">
@@ -775,19 +737,16 @@
         <v>0.01</v>
       </c>
       <c r="D12" t="n">
-        <v>-993.6614696</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E12" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G12" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="13">
@@ -803,19 +762,16 @@
         <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>-993.5717496000001</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E13" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G13" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="14">
@@ -831,19 +787,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-919.7270679999999</v>
+        <v>4386.4806544967</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02743</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3716713794276932</v>
+      </c>
       <c r="G14" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387261656163</v>
       </c>
     </row>
     <row r="15">
@@ -859,19 +812,16 @@
         <v>0.001</v>
       </c>
       <c r="D15" t="n">
-        <v>-919.701922</v>
+        <v>4386.4806544967</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02743</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3716713794276932</v>
+      </c>
       <c r="G15" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387261656163</v>
       </c>
     </row>
     <row r="16">
@@ -887,19 +837,16 @@
         <v>0.01</v>
       </c>
       <c r="D16" t="n">
-        <v>-919.6016254</v>
+        <v>4386.4806544967</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02748200000000001</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3716713794276932</v>
+      </c>
       <c r="G16" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387261656163</v>
       </c>
     </row>
     <row r="17">
@@ -915,19 +862,16 @@
         <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>-901.1297122</v>
+        <v>4386.194178599864</v>
       </c>
       <c r="E17" t="n">
-        <v>0.033072</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3715900678845767</v>
+      </c>
       <c r="G17" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387265237184</v>
       </c>
     </row>
     <row r="18">
@@ -943,21 +887,16 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>4393.075124</v>
+        <v>4394.132635548711</v>
       </c>
       <c r="E18" t="n">
-        <v>0.00182</v>
+        <v>0.00156</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1400195681746182</v>
+        <v>0.1320724925650147</v>
       </c>
       <c r="G18" t="n">
-        <v>28.10675799848774</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.5655440190625463</v>
       </c>
     </row>
     <row r="19">
@@ -973,21 +912,16 @@
         <v>0.001</v>
       </c>
       <c r="D19" t="n">
-        <v>4393.074857400001</v>
+        <v>4394.132558684796</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00182</v>
+        <v>0.00156</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1399695585304244</v>
+        <v>0.1320724925650147</v>
       </c>
       <c r="G19" t="n">
-        <v>28.10675800780129</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.5655440190625463</v>
       </c>
     </row>
     <row r="20">
@@ -1003,21 +937,16 @@
         <v>0.01</v>
       </c>
       <c r="D20" t="n">
-        <v>4393.072150599999</v>
+        <v>4394.203356010839</v>
       </c>
       <c r="E20" t="n">
-        <v>0.00182</v>
+        <v>0.00156</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1325867319289382</v>
+        <v>0.1319139374916282</v>
       </c>
       <c r="G20" t="n">
-        <v>28.10675800314478</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.1299852936770769</v>
       </c>
     </row>
     <row r="21">
@@ -1033,21 +962,16 @@
         <v>0.1</v>
       </c>
       <c r="D21" t="n">
-        <v>4377.453833199999</v>
+        <v>4386.011300615966</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5080660000000001</v>
+        <v>0.00143</v>
       </c>
       <c r="F21" t="n">
-        <v>0.06423448655329846</v>
+        <v>0.03914370030651567</v>
       </c>
       <c r="G21" t="n">
-        <v>28.10675816150107</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.6941031851628061</v>
       </c>
     </row>
     <row r="22">
@@ -1063,21 +987,16 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>4393.85939</v>
+        <v>4392.362755343318</v>
       </c>
       <c r="E22" t="n">
-        <v>0.00156</v>
+        <v>0.00182</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2090710596924913</v>
+        <v>-0.1955358070480275</v>
       </c>
       <c r="G22" t="n">
-        <v>28.21153617319812</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>6.754610276569707</v>
       </c>
     </row>
     <row r="23">
@@ -1093,21 +1012,16 @@
         <v>0.001</v>
       </c>
       <c r="D23" t="n">
-        <v>4393.859494</v>
+        <v>4392.392907872796</v>
       </c>
       <c r="E23" t="n">
-        <v>0.00156</v>
+        <v>0.00182</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2090439788943351</v>
+        <v>-0.1920084171909632</v>
       </c>
       <c r="G23" t="n">
-        <v>28.21153418989838</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>6.755889627365946</v>
       </c>
     </row>
     <row r="24">
@@ -1123,21 +1037,16 @@
         <v>0.01</v>
       </c>
       <c r="D24" t="n">
-        <v>4393.861246400001</v>
+        <v>4392.299647094682</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00156</v>
+        <v>0.00182</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2038883875915494</v>
+        <v>-0.1949793466364478</v>
       </c>
       <c r="G24" t="n">
-        <v>28.21151654679847</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>6.754080926425296</v>
       </c>
     </row>
     <row r="25">
@@ -1153,21 +1062,16 @@
         <v>0.1</v>
       </c>
       <c r="D25" t="n">
-        <v>4384.851077000001</v>
+        <v>4377.224143151194</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5078060000000001</v>
+        <v>0.00169</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.01649174151720318</v>
+        <v>-0.2201341903584148</v>
       </c>
       <c r="G25" t="n">
-        <v>28.21134309742261</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>5.944842716456527</v>
       </c>
     </row>
     <row r="26">
@@ -1183,21 +1087,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>4395.339621</v>
+        <v>4390.541984945536</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0.0009100000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1995944312471936</v>
+        <v>-0.2338470033820603</v>
       </c>
       <c r="G26" t="n">
-        <v>28.14849589455265</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>1.321161444352938</v>
       </c>
     </row>
     <row r="27">
@@ -1213,21 +1112,16 @@
         <v>0.001</v>
       </c>
       <c r="D27" t="n">
-        <v>4395.3703616</v>
+        <v>4390.628990858793</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0.0009100000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1989866795526699</v>
+        <v>-0.2302722496231941</v>
       </c>
       <c r="G27" t="n">
-        <v>28.14849599339213</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>1.342496565385925</v>
       </c>
     </row>
     <row r="28">
@@ -1243,21 +1137,16 @@
         <v>0.01</v>
       </c>
       <c r="D28" t="n">
-        <v>4395.1447044</v>
+        <v>4390.613286431879</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0.0009100000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.203884027335105</v>
+        <v>-0.2259706261883899</v>
       </c>
       <c r="G28" t="n">
-        <v>28.14849678430959</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>1.344062325325353</v>
       </c>
     </row>
     <row r="29">
@@ -1273,21 +1162,16 @@
         <v>0.1</v>
       </c>
       <c r="D29" t="n">
-        <v>4384.5232378</v>
+        <v>4382.731137512252</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4706260000000001</v>
+        <v>0.0006500000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.07497188944267656</v>
+        <v>-0.1928528644449911</v>
       </c>
       <c r="G29" t="n">
-        <v>28.14850426845662</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>0.6075590278557321</v>
       </c>
     </row>
     <row r="30">
@@ -1303,19 +1187,14 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>3632.254983</v>
+        <v>3547.501509933732</v>
       </c>
       <c r="E30" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>28.08849064738981</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.89226157029793</v>
       </c>
     </row>
     <row r="31">
@@ -1331,19 +1210,14 @@
         <v>0.001</v>
       </c>
       <c r="D31" t="n">
-        <v>3632.4300742</v>
+        <v>3547.276380780153</v>
       </c>
       <c r="E31" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
-        <v>28.0884908336629</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.89226193405601</v>
       </c>
     </row>
     <row r="32">
@@ -1359,19 +1233,14 @@
         <v>0.01</v>
       </c>
       <c r="D32" t="n">
-        <v>3607.726973</v>
+        <v>3516.656774188392</v>
       </c>
       <c r="E32" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
-        <v>28.0884926746456</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.78720257057489</v>
       </c>
     </row>
     <row r="33">
@@ -1387,19 +1256,14 @@
         <v>0.1</v>
       </c>
       <c r="D33" t="n">
-        <v>3533.9844408</v>
+        <v>3503.949663843028</v>
       </c>
       <c r="E33" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
-        <v>28.08851797662009</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.43696051113231</v>
       </c>
     </row>
   </sheetData>
@@ -1413,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1423,7 +1287,6 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1459,12 +1322,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Overshoot (V)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>run_name</t>
+          <t>Real Overshoot (V)</t>
         </is>
       </c>
     </row>
@@ -1481,19 +1339,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>3241.606678</v>
+        <v>4360.844031203538</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.005994573244089537</v>
+      </c>
       <c r="G2" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.33674190160272</v>
       </c>
     </row>
     <row r="3">
@@ -1509,19 +1364,16 @@
         <v>0.001</v>
       </c>
       <c r="D3" t="n">
-        <v>3242.1131194</v>
+        <v>4360.844036806375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.006101344503325805</v>
+      </c>
       <c r="G3" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.33674190162512</v>
       </c>
     </row>
     <row r="4">
@@ -1537,19 +1389,16 @@
         <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>3242.5902914</v>
+        <v>4360.948740590364</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-0.01112239662565145</v>
+      </c>
       <c r="G4" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.33411037797238</v>
       </c>
     </row>
     <row r="5">
@@ -1565,19 +1414,16 @@
         <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>-941.1559734</v>
+        <v>4364.283493865281</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03302000000000001</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0.0026</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.005799105331187916</v>
+      </c>
       <c r="G5" t="n">
-        <v>29.06855057684472</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.000</t>
-        </is>
+        <v>12.34249657405651</v>
       </c>
     </row>
     <row r="6">
@@ -1593,19 +1439,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7.498788</v>
+        <v>4338.47444504546</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>0.00923</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1316403671838796</v>
+      </c>
       <c r="G6" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>98.69644747121845</v>
       </c>
     </row>
     <row r="7">
@@ -1621,19 +1464,16 @@
         <v>0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>7.498788</v>
+        <v>4338.47444504546</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5198700000000001</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0.00923</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1316403671838796</v>
+      </c>
       <c r="G7" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>98.69644747121845</v>
       </c>
     </row>
     <row r="8">
@@ -1649,19 +1489,16 @@
         <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>-185.8635298</v>
+        <v>4338.47444504546</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4217460000000001</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0.00923</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1316403671838796</v>
+      </c>
       <c r="G8" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>98.69644747121845</v>
       </c>
     </row>
     <row r="9">
@@ -1677,19 +1514,14 @@
         <v>0.1</v>
       </c>
       <c r="D9" t="n">
-        <v>-992.4983909999999</v>
+        <v>-735.7867907523178</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02886000000000001</v>
+        <v>0.04134</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.001</t>
-        </is>
+        <v>100.2505162616509</v>
       </c>
     </row>
     <row r="10">
@@ -1705,19 +1537,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-993.661658</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E10" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G10" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="11">
@@ -1733,19 +1562,16 @@
         <v>0.001</v>
       </c>
       <c r="D11" t="n">
-        <v>-993.661658</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G11" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="12">
@@ -1761,19 +1587,16 @@
         <v>0.01</v>
       </c>
       <c r="D12" t="n">
-        <v>-993.6614696</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E12" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G12" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="13">
@@ -1789,19 +1612,16 @@
         <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>-993.5717496000001</v>
+        <v>4366.437274191179</v>
       </c>
       <c r="E13" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0.00559</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1284536634591455</v>
+      </c>
       <c r="G13" t="n">
-        <v>28.30341977999458</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.010</t>
-        </is>
+        <v>43.77735617585954</v>
       </c>
     </row>
     <row r="14">
@@ -1817,19 +1637,16 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-919.7270679999999</v>
+        <v>4386.4806544967</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02743</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3716713794276932</v>
+      </c>
       <c r="G14" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387261656163</v>
       </c>
     </row>
     <row r="15">
@@ -1845,19 +1662,16 @@
         <v>0.001</v>
       </c>
       <c r="D15" t="n">
-        <v>-919.701922</v>
+        <v>4386.4806544967</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02743</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3716713794276932</v>
+      </c>
       <c r="G15" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387261656163</v>
       </c>
     </row>
     <row r="16">
@@ -1873,19 +1687,16 @@
         <v>0.01</v>
       </c>
       <c r="D16" t="n">
-        <v>-919.6016254</v>
+        <v>4386.4806544967</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02748200000000001</v>
-      </c>
-      <c r="F16" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3716713794276932</v>
+      </c>
       <c r="G16" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387261656163</v>
       </c>
     </row>
     <row r="17">
@@ -1901,19 +1712,16 @@
         <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>-901.1297122</v>
+        <v>4386.194178599864</v>
       </c>
       <c r="E17" t="n">
-        <v>0.033072</v>
-      </c>
-      <c r="F17" t="inlineStr"/>
+        <v>0.00273</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3715900678845767</v>
+      </c>
       <c r="G17" t="n">
-        <v>29.30336751562852</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>dqn_noise_0.100</t>
-        </is>
+        <v>14.37387265237184</v>
       </c>
     </row>
   </sheetData>
@@ -1927,7 +1735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1937,7 +1745,6 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1973,12 +1780,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Overshoot (V)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>run_name</t>
+          <t>Real Overshoot (V)</t>
         </is>
       </c>
     </row>
@@ -1995,21 +1797,16 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>4393.075124</v>
+        <v>4394.132635548711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00182</v>
+        <v>0.00156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1400195681746182</v>
+        <v>0.1320724925650147</v>
       </c>
       <c r="G2" t="n">
-        <v>28.10675799848774</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.5655440190625463</v>
       </c>
     </row>
     <row r="3">
@@ -2025,21 +1822,16 @@
         <v>0.001</v>
       </c>
       <c r="D3" t="n">
-        <v>4393.074857400001</v>
+        <v>4394.132558684796</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00182</v>
+        <v>0.00156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1399695585304244</v>
+        <v>0.1320724925650147</v>
       </c>
       <c r="G3" t="n">
-        <v>28.10675800780129</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.5655440190625463</v>
       </c>
     </row>
     <row r="4">
@@ -2055,21 +1847,16 @@
         <v>0.01</v>
       </c>
       <c r="D4" t="n">
-        <v>4393.072150599999</v>
+        <v>4394.203356010839</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00182</v>
+        <v>0.00156</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1325867319289382</v>
+        <v>0.1319139374916282</v>
       </c>
       <c r="G4" t="n">
-        <v>28.10675800314478</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.1299852936770769</v>
       </c>
     </row>
     <row r="5">
@@ -2085,21 +1872,16 @@
         <v>0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>4377.453833199999</v>
+        <v>4386.011300615966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5080660000000001</v>
+        <v>0.00143</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06423448655329846</v>
+        <v>0.03914370030651567</v>
       </c>
       <c r="G5" t="n">
-        <v>28.10675816150107</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>td3_noise_0.000</t>
-        </is>
+        <v>0.6941031851628061</v>
       </c>
     </row>
     <row r="6">
@@ -2115,21 +1897,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>4393.85939</v>
+        <v>4392.362755343318</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00156</v>
+        <v>0.00182</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2090710596924913</v>
+        <v>-0.1955358070480275</v>
       </c>
       <c r="G6" t="n">
-        <v>28.21153617319812</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>6.754610276569707</v>
       </c>
     </row>
     <row r="7">
@@ -2145,21 +1922,16 @@
         <v>0.001</v>
       </c>
       <c r="D7" t="n">
-        <v>4393.859494</v>
+        <v>4392.392907872796</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00156</v>
+        <v>0.00182</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2090439788943351</v>
+        <v>-0.1920084171909632</v>
       </c>
       <c r="G7" t="n">
-        <v>28.21153418989838</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>6.755889627365946</v>
       </c>
     </row>
     <row r="8">
@@ -2175,21 +1947,16 @@
         <v>0.01</v>
       </c>
       <c r="D8" t="n">
-        <v>4393.861246400001</v>
+        <v>4392.299647094682</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00156</v>
+        <v>0.00182</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2038883875915494</v>
+        <v>-0.1949793466364478</v>
       </c>
       <c r="G8" t="n">
-        <v>28.21151654679847</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>6.754080926425296</v>
       </c>
     </row>
     <row r="9">
@@ -2205,21 +1972,16 @@
         <v>0.1</v>
       </c>
       <c r="D9" t="n">
-        <v>4384.851077000001</v>
+        <v>4377.224143151194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5078060000000001</v>
+        <v>0.00169</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.01649174151720318</v>
+        <v>-0.2201341903584148</v>
       </c>
       <c r="G9" t="n">
-        <v>28.21134309742261</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>td3_noise_0.001</t>
-        </is>
+        <v>5.944842716456527</v>
       </c>
     </row>
     <row r="10">
@@ -2235,21 +1997,16 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>4395.339621</v>
+        <v>4390.541984945536</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0.0009100000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1995944312471936</v>
+        <v>-0.2338470033820603</v>
       </c>
       <c r="G10" t="n">
-        <v>28.14849589455265</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>1.321161444352938</v>
       </c>
     </row>
     <row r="11">
@@ -2265,21 +2022,16 @@
         <v>0.001</v>
       </c>
       <c r="D11" t="n">
-        <v>4395.3703616</v>
+        <v>4390.628990858793</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0.0009100000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1989866795526699</v>
+        <v>-0.2302722496231941</v>
       </c>
       <c r="G11" t="n">
-        <v>28.14849599339213</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>1.342496565385925</v>
       </c>
     </row>
     <row r="12">
@@ -2295,21 +2047,16 @@
         <v>0.01</v>
       </c>
       <c r="D12" t="n">
-        <v>4395.1447044</v>
+        <v>4390.613286431879</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0006500000000000001</v>
+        <v>0.0009100000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.203884027335105</v>
+        <v>-0.2259706261883899</v>
       </c>
       <c r="G12" t="n">
-        <v>28.14849678430959</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>1.344062325325353</v>
       </c>
     </row>
     <row r="13">
@@ -2325,21 +2072,16 @@
         <v>0.1</v>
       </c>
       <c r="D13" t="n">
-        <v>4384.5232378</v>
+        <v>4382.731137512252</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4706260000000001</v>
+        <v>0.0006500000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.07497188944267656</v>
+        <v>-0.1928528644449911</v>
       </c>
       <c r="G13" t="n">
-        <v>28.14850426845662</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>td3_noise_0.010</t>
-        </is>
+        <v>0.6075590278557321</v>
       </c>
     </row>
     <row r="14">
@@ -2355,19 +2097,14 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>3632.254983</v>
+        <v>3547.501509933732</v>
       </c>
       <c r="E14" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>28.08849064738981</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.89226157029793</v>
       </c>
     </row>
     <row r="15">
@@ -2383,19 +2120,14 @@
         <v>0.001</v>
       </c>
       <c r="D15" t="n">
-        <v>3632.4300742</v>
+        <v>3547.276380780153</v>
       </c>
       <c r="E15" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>28.0884908336629</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.89226193405601</v>
       </c>
     </row>
     <row r="16">
@@ -2411,19 +2143,14 @@
         <v>0.01</v>
       </c>
       <c r="D16" t="n">
-        <v>3607.726973</v>
+        <v>3516.656774188392</v>
       </c>
       <c r="E16" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>28.0884926746456</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.78720257057489</v>
       </c>
     </row>
     <row r="17">
@@ -2439,19 +2166,14 @@
         <v>0.1</v>
       </c>
       <c r="D17" t="n">
-        <v>3533.9844408</v>
+        <v>3503.949663843028</v>
       </c>
       <c r="E17" t="n">
         <v>0.5198700000000001</v>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>28.08851797662009</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>td3_noise_0.100</t>
-        </is>
+        <v>38.43696051113231</v>
       </c>
     </row>
   </sheetData>
